--- a/data/trans_camb/P19C07-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P19C07-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 5,47</t>
+          <t>-1,1; 5,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 6,84</t>
+          <t>0,13; 7,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 12,79</t>
+          <t>0,77; 13,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 6,29</t>
+          <t>-0,38; 6,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,14; 10,14</t>
+          <t>2,52; 10,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 9,23</t>
+          <t>1,27; 8,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 4,78</t>
+          <t>0,26; 4,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,14; 7,25</t>
+          <t>2,17; 7,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 9,2</t>
+          <t>2,36; 9,08</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-49,08; 712,03</t>
+          <t>-48,56; 857,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-18,9; 936,4</t>
+          <t>-16,02; 1011,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,89; 1593,81</t>
+          <t>-11,27; 1725,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-40,77; 1059,84</t>
+          <t>-26,73; 961,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,57; 1620,02</t>
+          <t>43,45; 1627,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,19; 1411,06</t>
+          <t>9,74; 1188,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,8; 465,28</t>
+          <t>0,49; 488,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>49,55; 717,59</t>
+          <t>58,33; 717,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65,02; 888,2</t>
+          <t>53,62; 837,35</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 3,98</t>
+          <t>-1,44; 4,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 1,66</t>
+          <t>-3,19; 1,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 3,34</t>
+          <t>-1,89; 3,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 0,91</t>
+          <t>-4,06; 1,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 0,66</t>
+          <t>-4,3; 0,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 4,02</t>
+          <t>-1,57; 4,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,64</t>
+          <t>-1,92; 1,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 0,32</t>
+          <t>-2,84; 0,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 2,91</t>
+          <t>-0,88; 2,79</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-36,4; 218,59</t>
+          <t>-37,06; 209,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-75,21; 105,87</t>
+          <t>-74,14; 86,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-45,54; 187,39</t>
+          <t>-48,35; 168,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-76,07; 34,64</t>
+          <t>-72,56; 46,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-74,41; 29,52</t>
+          <t>-73,03; 34,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,55; 141,88</t>
+          <t>-29,98; 140,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-44,27; 61,06</t>
+          <t>-41,8; 60,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-63,68; 13,86</t>
+          <t>-64,33; 19,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-21,27; 107,61</t>
+          <t>-20,34; 105,95</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 3,18</t>
+          <t>-1,56; 3,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 3,85</t>
+          <t>-1,04; 4,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 2,68</t>
+          <t>-1,88; 2,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 4,56</t>
+          <t>-0,72; 4,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 4,01</t>
+          <t>-1,19; 4,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 1,49</t>
+          <t>-2,56; 1,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 3,23</t>
+          <t>-0,43; 3,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 3,11</t>
+          <t>-0,51; 3,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 1,56</t>
+          <t>-1,79; 1,43</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-62,8; 579,42</t>
+          <t>-61,97; 586,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-60,35; 596,45</t>
+          <t>-55,13; 656,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-76,55; 577,44</t>
+          <t>-73,74; 552,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-31,04; 481,24</t>
+          <t>-37,06; 457,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-50,13; 476,63</t>
+          <t>-47,71; 409,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-70,12; 206,72</t>
+          <t>-71,72; 192,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 328,18</t>
+          <t>-21,32; 302,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,09; 291,45</t>
+          <t>-23,39; 277,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-59,33; 145,95</t>
+          <t>-64,61; 145,94</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 3,28</t>
+          <t>-3,07; 3,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 2,43</t>
+          <t>-3,36; 2,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 3,08</t>
+          <t>-4,22; 2,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 1,94</t>
+          <t>-5,16; 1,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,99; -0,51</t>
+          <t>-6,61; -0,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,86; -2,15</t>
+          <t>-7,83; -1,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 1,26</t>
+          <t>-3,31; 1,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 0,1</t>
+          <t>-4,53; -0,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,57; -1,07</t>
+          <t>-5,27; -1,02</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-70,95; 222,99</t>
+          <t>-68,65; 201,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-74,92; 196,86</t>
+          <t>-74,46; 181,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-94,08; 353,42</t>
+          <t>-94,99; 247,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-65,95; 52,65</t>
+          <t>-63,15; 39,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-80,87; -6,73</t>
+          <t>-79,88; 3,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-91,5; -43,4</t>
+          <t>-91,91; -39,76</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-57,8; 38,64</t>
+          <t>-56,82; 47,96</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-67,79; 8,7</t>
+          <t>-73,4; -2,45</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-87,56; -19,92</t>
+          <t>-85,59; -25,11</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 1,52</t>
+          <t>-6,36; 1,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 5,52</t>
+          <t>-4,37; 6,34</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 1,65</t>
+          <t>-6,09; 2,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 2,9</t>
+          <t>-4,93; 2,97</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 3,71</t>
+          <t>-4,03; 4,11</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 2,43</t>
+          <t>-5,01; 2,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 1,01</t>
+          <t>-4,5; 0,99</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 3,26</t>
+          <t>-3,38; 3,09</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 0,92</t>
+          <t>-4,21; 1,15</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-83,18; 83,46</t>
+          <t>-88,47; 83,28</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-68,08; 199,11</t>
+          <t>-67,44; 254,11</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-83,19; 82,39</t>
+          <t>-82,91; 98,4</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-79,87; 218,18</t>
+          <t>-81,66; 202,53</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-79,07; 227,08</t>
+          <t>-74,85; 231,64</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-76,08; 160,24</t>
+          <t>-74,35; 180,22</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-70,56; 43,51</t>
+          <t>-73,58; 46,29</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-54,1; 133,26</t>
+          <t>-60,0; 104,23</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-70,41; 37,75</t>
+          <t>-68,14; 61,36</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 4,46</t>
+          <t>-0,55; 4,55</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 2,81</t>
+          <t>-1,68; 2,75</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 3,46</t>
+          <t>-1,08; 3,32</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 6,1</t>
+          <t>-0,51; 6,06</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,68; 7,6</t>
+          <t>0,89; 7,8</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 1,27</t>
+          <t>-3,12; 1,19</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,34; 4,63</t>
+          <t>0,3; 4,52</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,3</t>
+          <t>0,48; 4,36</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 1,6</t>
+          <t>-1,46; 1,74</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-63,89; —</t>
+          <t>-47,92; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1873,37 +1873,37 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-89,83; —</t>
+          <t>-87,74; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-33,22; 967,83</t>
+          <t>-33,33; 965,05</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1,39; 1067,03</t>
+          <t>-1,31; 1069,53</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-90,6; 265,39</t>
+          <t>-85,11; 207,15</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 576,35</t>
+          <t>-4,69; 649,11</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>6,27; 639,23</t>
+          <t>6,12; 637,3</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-68,0; 260,88</t>
+          <t>-63,08; 312,16</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 2,69</t>
+          <t>-2,28; 2,61</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,3; -0,15</t>
+          <t>-4,57; -0,4</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 2,4</t>
+          <t>-2,42; 2,21</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 1,77</t>
+          <t>-2,03; 1,63</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 1,5</t>
+          <t>-2,63; 1,51</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 4,1</t>
+          <t>-1,57; 4,13</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 1,53</t>
+          <t>-1,7; 1,5</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 0,04</t>
+          <t>-2,79; 0,05</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 2,51</t>
+          <t>-1,47; 2,39</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-49,41; 107,97</t>
+          <t>-47,79; 104,45</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-87,03; -0,33</t>
+          <t>-87,68; -7,85</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-53,01; 101,52</t>
+          <t>-49,91; 97,29</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-53,61; 107,93</t>
+          <t>-52,75; 87,59</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-67,96; 92,49</t>
+          <t>-66,11; 84,29</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-37,84; 204,16</t>
+          <t>-36,01; 201,98</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-38,86; 64,63</t>
+          <t>-42,38; 59,19</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-69,13; 2,96</t>
+          <t>-70,66; 3,59</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-27,99; 95,82</t>
+          <t>-33,28; 92,56</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,98; -0,14</t>
+          <t>-5,07; -0,13</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 0,34</t>
+          <t>-4,72; 0,4</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-5,74; -0,25</t>
+          <t>-5,76; -0,34</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 2,47</t>
+          <t>-1,98; 2,06</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 1,68</t>
+          <t>-2,45; 1,76</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 3,03</t>
+          <t>-1,19; 3,14</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 0,42</t>
+          <t>-2,74; 0,45</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 0,24</t>
+          <t>-2,78; 0,39</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 0,82</t>
+          <t>-2,83; 0,91</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-69,87; 0,97</t>
+          <t>-68,82; 1,19</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-65,31; 9,69</t>
+          <t>-67,54; 12,88</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-80,8; -6,36</t>
+          <t>-81,05; -9,43</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-42,42; 93,31</t>
+          <t>-42,65; 75,29</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-53,73; 65,06</t>
+          <t>-52,55; 63,09</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-28,41; 113,85</t>
+          <t>-27,57; 124,75</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-51,01; 12,48</t>
+          <t>-49,42; 12,9</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-49,22; 7,56</t>
+          <t>-50,38; 11,31</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-54,83; 21,07</t>
+          <t>-51,39; 22,71</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,94</t>
+          <t>-1,13; 0,86</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,42</t>
+          <t>-1,69; 0,31</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,92</t>
+          <t>-1,42; 0,91</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,11</t>
+          <t>-0,83; 1,09</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,13</t>
+          <t>-0,76; 1,05</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,36</t>
+          <t>-0,72; 1,35</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,75</t>
+          <t>-0,7; 0,73</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,48</t>
+          <t>-0,95; 0,52</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,88</t>
+          <t>-0,8; 0,81</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-27,19; 31,98</t>
+          <t>-28,29; 30,2</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-38,87; 15,33</t>
+          <t>-41,09; 11,97</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-34,45; 31,48</t>
+          <t>-36,79; 31,03</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-21,98; 37,9</t>
+          <t>-20,56; 36,2</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-21,9; 38,23</t>
+          <t>-19,29; 34,3</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-18,42; 44,81</t>
+          <t>-18,2; 44,64</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-16,74; 24,27</t>
+          <t>-18,08; 24,48</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-24,06; 15,79</t>
+          <t>-25,08; 16,3</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-18,51; 28,23</t>
+          <t>-21,08; 26,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C07-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P19C07-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,04</t>
+          <t>3,32</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,9</t>
+          <t>4,17</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,98</t>
+          <t>3,75</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 5,63</t>
+          <t>-1,42; 4,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 7,03</t>
+          <t>0,08; 7,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 13,28</t>
+          <t>0,24; 8,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 6,33</t>
+          <t>-0,82; 6,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 10,14</t>
+          <t>2,38; 9,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 8,6</t>
+          <t>1,02; 7,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 4,87</t>
+          <t>0,06; 5,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 7,25</t>
+          <t>2,25; 7,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 9,08</t>
+          <t>1,31; 6,38</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>259,09%</t>
+          <t>170,44%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>256,55%</t>
+          <t>217,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>258,05%</t>
+          <t>194,34%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-48,56; 857,06</t>
+          <t>-56,73; 716,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,02; 1011,28</t>
+          <t>-21,49; 1131,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 1725,59</t>
+          <t>-17,42; 1106,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-26,73; 961,73</t>
+          <t>-39,47; 904,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>43,45; 1627,84</t>
+          <t>33,91; 1471,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,74; 1188,23</t>
+          <t>-7,13; 1301,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 488,39</t>
+          <t>-15,01; 465,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>58,33; 717,96</t>
+          <t>61,82; 705,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>53,62; 837,35</t>
+          <t>21,56; 545,18</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>1,24</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 4,09</t>
+          <t>-1,27; 3,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 1,34</t>
+          <t>-3,23; 1,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 3,09</t>
+          <t>-1,87; 2,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 1,04</t>
+          <t>-4,28; 0,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 0,85</t>
+          <t>-4,06; 0,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 4,04</t>
+          <t>-1,18; 4,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 1,65</t>
+          <t>-2,14; 1,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 0,48</t>
+          <t>-3,02; 0,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 2,79</t>
+          <t>-1,01; 2,74</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,48%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-37,06; 209,38</t>
+          <t>-34,47; 201,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-74,14; 86,7</t>
+          <t>-74,34; 77,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-48,35; 168,04</t>
+          <t>-47,96; 154,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-72,56; 46,26</t>
+          <t>-74,8; 40,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-73,03; 34,1</t>
+          <t>-74,22; 19,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,98; 140,98</t>
+          <t>-26,81; 141,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-41,8; 60,82</t>
+          <t>-46,79; 53,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,33; 19,92</t>
+          <t>-65,39; 23,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 105,95</t>
+          <t>-23,16; 99,59</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>-0,29</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,01</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,31</t>
+          <t>-1,49; 3,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 4,1</t>
+          <t>-1,04; 4,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 2,82</t>
+          <t>-1,82; 2,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 4,48</t>
+          <t>-0,7; 4,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 4,16</t>
+          <t>-1,03; 4,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 1,47</t>
+          <t>-2,65; 1,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 3,25</t>
+          <t>-0,28; 3,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 3,28</t>
+          <t>-0,43; 3,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,43</t>
+          <t>-1,55; 1,53</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-12,22%</t>
+          <t>-14,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-61,97; 586,85</t>
+          <t>-56,45; 596,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-55,13; 656,03</t>
+          <t>-45,71; 842,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-73,74; 552,19</t>
+          <t>-76,84; 507,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-37,06; 457,74</t>
+          <t>-29,74; 465,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-47,71; 409,42</t>
+          <t>-44,95; 394,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-71,72; 192,66</t>
+          <t>-76,65; 153,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-21,32; 302,06</t>
+          <t>-15,21; 303,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,39; 277,81</t>
+          <t>-25,21; 307,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-64,61; 145,94</t>
+          <t>-57,8; 140,86</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,33</t>
+          <t>-1,45</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-4,73</t>
+          <t>-4,09</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-3,15</t>
+          <t>-2,84</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 3,33</t>
+          <t>-3,08; 3,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 2,44</t>
+          <t>-3,3; 2,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 2,43</t>
+          <t>-4,05; 2,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 1,56</t>
+          <t>-4,95; 2,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,61; -0,12</t>
+          <t>-6,55; -0,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,83; -1,92</t>
+          <t>-7,24; -1,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 1,64</t>
+          <t>-3,24; 1,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,53; -0,16</t>
+          <t>-4,07; -0,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,27; -1,02</t>
+          <t>-4,98; -0,52</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-43,29%</t>
+          <t>-47,43%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-77,44%</t>
+          <t>-66,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-67,46%</t>
+          <t>-60,84%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-68,65; 201,69</t>
+          <t>-67,76; 218,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-74,46; 181,52</t>
+          <t>-71,62; 179,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-94,99; 247,47</t>
+          <t>-94,4; 240,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-63,15; 39,64</t>
+          <t>-62,68; 54,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-79,88; 3,11</t>
+          <t>-80,58; 2,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-91,91; -39,76</t>
+          <t>-86,47; -19,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-56,82; 47,96</t>
+          <t>-56,19; 41,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-73,4; -2,45</t>
+          <t>-69,1; 4,54</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-85,59; -25,11</t>
+          <t>-82,74; -1,54</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-1,96</t>
+          <t>-2,12</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,92</t>
+          <t>-0,85</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,43</t>
+          <t>-1,47</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 1,58</t>
+          <t>-6,31; 1,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 6,34</t>
+          <t>-4,47; 5,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 2,05</t>
+          <t>-6,58; 1,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 2,97</t>
+          <t>-5,11; 2,97</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 4,11</t>
+          <t>-4,34; 3,94</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 2,61</t>
+          <t>-4,92; 2,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 0,99</t>
+          <t>-4,46; 1,11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 3,09</t>
+          <t>-3,2; 3,39</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 1,15</t>
+          <t>-4,2; 1,05</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-40,43%</t>
+          <t>-43,72%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-24,13%</t>
+          <t>-22,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-33,16%</t>
+          <t>-34,06%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-88,47; 83,28</t>
+          <t>-85,72; 46,4</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-67,44; 254,11</t>
+          <t>-68,13; 200,03</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-82,91; 98,4</t>
+          <t>-82,85; 75,13</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-81,66; 202,53</t>
+          <t>-80,41; 196,72</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-74,85; 231,64</t>
+          <t>-72,94; 261,94</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-74,35; 180,22</t>
+          <t>-77,77; 204,64</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-73,58; 46,29</t>
+          <t>-71,82; 47,05</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-60,0; 104,23</t>
+          <t>-56,94; 122,61</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-68,14; 61,36</t>
+          <t>-69,09; 49,94</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-0,62</t>
+          <t>-0,63</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,07</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 4,55</t>
+          <t>-0,74; 4,22</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 2,75</t>
+          <t>-1,48; 2,64</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 3,32</t>
+          <t>-1,08; 3,29</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 6,06</t>
+          <t>-0,4; 6,55</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,89; 7,8</t>
+          <t>0,69; 7,61</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 1,19</t>
+          <t>-3,31; 1,1</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,3; 4,52</t>
+          <t>0,17; 4,49</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,36</t>
+          <t>0,23; 4,3</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,74</t>
+          <t>-1,52; 1,54</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-31,99%</t>
+          <t>-32,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-47,92; —</t>
+          <t>-66,74; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1873,37 +1873,37 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-87,74; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-33,33; 965,05</t>
+          <t>-30,7; 883,67</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 1069,53</t>
+          <t>8,78; 1056,91</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-85,11; 207,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 649,11</t>
+          <t>-5,21; 664,43</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>6,12; 637,3</t>
+          <t>-8,16; 611,21</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-63,08; 312,16</t>
+          <t>-67,22; 245,6</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,2</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,48</t>
+          <t>2,84</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,74</t>
+          <t>1,8</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 2,61</t>
+          <t>-2,37; 2,58</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,57; -0,4</t>
+          <t>-4,45; -0,22</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 2,21</t>
+          <t>-1,98; 3,29</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 1,63</t>
+          <t>-2,21; 1,52</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 1,51</t>
+          <t>-2,48; 1,54</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 4,13</t>
+          <t>0,61; 5,22</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 1,5</t>
+          <t>-1,57; 1,45</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 0,05</t>
+          <t>-2,84; 0,12</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 2,39</t>
+          <t>-0,08; 3,42</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-5,43%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>55,16%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-47,79; 104,45</t>
+          <t>-48,33; 107,83</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-87,68; -7,85</t>
+          <t>-85,53; 3,91</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-49,91; 97,29</t>
+          <t>-42,71; 133,11</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-52,75; 87,59</t>
+          <t>-55,35; 82,12</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-66,11; 84,29</t>
+          <t>-64,41; 84,21</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-36,01; 201,98</t>
+          <t>10,07; 289,68</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-42,38; 59,19</t>
+          <t>-39,02; 57,5</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-70,66; 3,59</t>
+          <t>-69,3; 8,11</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-33,28; 92,56</t>
+          <t>-2,23; 134,68</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-2,58</t>
+          <t>-1,37</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-0,87</t>
+          <t>-0,19</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-5,07; -0,13</t>
+          <t>-4,78; -0,29</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 0,4</t>
+          <t>-4,81; 0,15</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-5,76; -0,34</t>
+          <t>-4,0; 1,26</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 2,06</t>
+          <t>-2,14; 2,44</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 1,76</t>
+          <t>-2,61; 1,51</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 3,14</t>
+          <t>-1,18; 3,2</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 0,45</t>
+          <t>-2,58; 0,6</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 0,39</t>
+          <t>-2,86; 0,43</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 0,91</t>
+          <t>-1,88; 1,44</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-47,33%</t>
+          <t>-25,14%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-19,17%</t>
+          <t>-4,18%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-68,82; 1,19</t>
+          <t>-69,46; -2,86</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-67,54; 12,88</t>
+          <t>-65,59; 7,16</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-81,05; -9,43</t>
+          <t>-58,73; 34,24</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-42,65; 75,29</t>
+          <t>-42,83; 93,84</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-52,55; 63,09</t>
+          <t>-53,86; 58,88</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-27,57; 124,75</t>
+          <t>-26,05; 121,52</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-49,42; 12,9</t>
+          <t>-46,96; 18,7</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-50,38; 11,31</t>
+          <t>-51,88; 12,61</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-51,39; 22,71</t>
+          <t>-35,03; 39,44</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-0,23</t>
+          <t>0,03</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,39</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,86</t>
+          <t>-1,05; 1,0</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 0,31</t>
+          <t>-1,54; 0,38</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 0,91</t>
+          <t>-0,96; 1,19</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,09</t>
+          <t>-0,82; 1,2</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,05</t>
+          <t>-0,88; 0,95</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 1,35</t>
+          <t>-0,3; 1,63</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,73</t>
+          <t>-0,7; 0,68</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,52</t>
+          <t>-0,97; 0,45</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,81</t>
+          <t>-0,31; 1,08</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-6,68%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-28,29; 30,2</t>
+          <t>-26,51; 36,49</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-41,09; 11,97</t>
+          <t>-38,13; 13,61</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-36,79; 31,03</t>
+          <t>-25,54; 41,22</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-20,56; 36,2</t>
+          <t>-20,95; 38,28</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-19,29; 34,3</t>
+          <t>-22,31; 32,1</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-18,2; 44,64</t>
+          <t>-7,7; 53,97</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-18,08; 24,48</t>
+          <t>-18,16; 21,51</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-25,08; 16,3</t>
+          <t>-25,63; 14,4</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-21,08; 26,05</t>
+          <t>-8,16; 34,74</t>
         </is>
       </c>
     </row>
